--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19137-2022 artfynd.xlsx
+++ b/artfynd/A 19137-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129012166</v>
       </c>
       <c r="B2" t="n">
-        <v>98644</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
